--- a/docs/Mapping_casi_uso/morte/Morte_005.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_005.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="220">
   <si>
     <t>Sezione</t>
   </si>
@@ -132,6 +132,12 @@
   </si>
   <si>
     <t>testoDataPresuntaMorte</t>
+  </si>
+  <si>
+    <t>Data rinvenimento cadavere</t>
+  </si>
+  <si>
+    <t>dataRinvenimentoCadavere</t>
   </si>
   <si>
     <t>Luogo</t>
@@ -724,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -1244,19 +1250,19 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>10</v>
@@ -1267,16 +1273,16 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>61</v>
@@ -1290,16 +1296,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>63</v>
@@ -1313,7 +1319,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>64</v>
@@ -1322,7 +1328,7 @@
         <v>27</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>65</v>
@@ -1336,16 +1342,16 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>67</v>
@@ -1359,16 +1365,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>69</v>
@@ -1382,7 +1388,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>70</v>
@@ -1391,7 +1397,7 @@
         <v>27</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>71</v>
@@ -1405,16 +1411,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>73</v>
@@ -1428,7 +1434,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>74</v>
@@ -1437,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>75</v>
@@ -1451,7 +1457,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>76</v>
@@ -1460,7 +1466,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>77</v>
@@ -1474,16 +1480,16 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>79</v>
@@ -1497,7 +1503,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>80</v>
@@ -1506,7 +1512,7 @@
         <v>27</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>81</v>
@@ -1520,7 +1526,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>82</v>
@@ -1529,7 +1535,7 @@
         <v>27</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>83</v>
@@ -1543,7 +1549,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>84</v>
@@ -1552,7 +1558,7 @@
         <v>27</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>85</v>
@@ -1566,7 +1572,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>86</v>
@@ -1575,7 +1581,7 @@
         <v>27</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>87</v>
@@ -1589,16 +1595,16 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>89</v>
@@ -1612,7 +1618,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>90</v>
@@ -1621,7 +1627,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>91</v>
@@ -1635,16 +1641,16 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>93</v>
@@ -1658,7 +1664,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>94</v>
@@ -1667,7 +1673,7 @@
         <v>27</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>95</v>
@@ -1681,7 +1687,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>96</v>
@@ -1690,7 +1696,7 @@
         <v>27</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>97</v>
@@ -1704,7 +1710,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>98</v>
@@ -1713,7 +1719,7 @@
         <v>27</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>99</v>
@@ -1727,7 +1733,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>100</v>
@@ -1736,7 +1742,7 @@
         <v>27</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>101</v>
@@ -1750,7 +1756,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>102</v>
@@ -1759,7 +1765,7 @@
         <v>27</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>103</v>
@@ -1773,7 +1779,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>104</v>
@@ -1782,7 +1788,7 @@
         <v>27</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>105</v>
@@ -1796,7 +1802,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>106</v>
@@ -1805,7 +1811,7 @@
         <v>27</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>107</v>
@@ -1819,7 +1825,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>108</v>
@@ -1828,7 +1834,7 @@
         <v>27</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>109</v>
@@ -1842,7 +1848,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>110</v>
@@ -1851,7 +1857,7 @@
         <v>27</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>111</v>
@@ -1865,7 +1871,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>112</v>
@@ -1874,7 +1880,7 @@
         <v>27</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>113</v>
@@ -1888,7 +1894,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>114</v>
@@ -1897,7 +1903,7 @@
         <v>27</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>115</v>
@@ -1911,19 +1917,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -1934,16 +1940,16 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>121</v>
@@ -1957,19 +1963,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
@@ -1980,16 +1986,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>127</v>
@@ -2003,7 +2009,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>128</v>
@@ -2012,7 +2018,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>129</v>
@@ -2026,19 +2032,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -2049,16 +2055,16 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>132</v>
@@ -2072,16 +2078,16 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>134</v>
@@ -2095,16 +2101,16 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>136</v>
@@ -2118,39 +2124,39 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C61" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>61</v>
@@ -2159,35 +2165,35 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>66</v>
@@ -2196,7 +2202,7 @@
         <v>27</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>67</v>
@@ -2205,12 +2211,12 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>68</v>
@@ -2219,7 +2225,7 @@
         <v>27</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>69</v>
@@ -2228,12 +2234,12 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>70</v>
@@ -2242,7 +2248,7 @@
         <v>27</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>71</v>
@@ -2251,12 +2257,12 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>72</v>
@@ -2265,7 +2271,7 @@
         <v>27</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>73</v>
@@ -2274,21 +2280,21 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>75</v>
@@ -2297,21 +2303,21 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>77</v>
@@ -2320,21 +2326,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>79</v>
@@ -2343,21 +2349,21 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>81</v>
@@ -2366,21 +2372,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>83</v>
@@ -2389,21 +2395,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>85</v>
@@ -2412,21 +2418,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>87</v>
@@ -2435,12 +2441,12 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>88</v>
@@ -2449,7 +2455,7 @@
         <v>27</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>89</v>
@@ -2458,21 +2464,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>91</v>
@@ -2481,67 +2487,67 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>95</v>
@@ -2550,21 +2556,21 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>97</v>
@@ -2573,21 +2579,21 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>99</v>
@@ -2596,21 +2602,21 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>101</v>
@@ -2619,21 +2625,21 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>103</v>
@@ -2642,21 +2648,21 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>105</v>
@@ -2665,21 +2671,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>107</v>
@@ -2688,35 +2694,35 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>158</v>
@@ -2725,7 +2731,7 @@
         <v>27</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>159</v>
@@ -2734,12 +2740,12 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>160</v>
@@ -2748,7 +2754,7 @@
         <v>27</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>161</v>
@@ -2757,44 +2763,44 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C89" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>61</v>
@@ -2803,35 +2809,35 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>66</v>
@@ -2840,7 +2846,7 @@
         <v>27</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>67</v>
@@ -2849,12 +2855,12 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>68</v>
@@ -2863,7 +2869,7 @@
         <v>27</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>69</v>
@@ -2872,12 +2878,12 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>70</v>
@@ -2886,7 +2892,7 @@
         <v>27</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>71</v>
@@ -2895,12 +2901,12 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>72</v>
@@ -2909,7 +2915,7 @@
         <v>27</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>73</v>
@@ -2918,21 +2924,21 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>75</v>
@@ -2941,21 +2947,21 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>77</v>
@@ -2964,21 +2970,21 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>79</v>
@@ -2987,21 +2993,21 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>81</v>
@@ -3010,21 +3016,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>83</v>
@@ -3033,21 +3039,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>85</v>
@@ -3056,21 +3062,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>87</v>
@@ -3079,12 +3085,12 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>88</v>
@@ -3093,7 +3099,7 @@
         <v>27</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>89</v>
@@ -3102,21 +3108,21 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>91</v>
@@ -3125,67 +3131,67 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>95</v>
@@ -3194,21 +3200,21 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>97</v>
@@ -3217,21 +3223,21 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>99</v>
@@ -3240,21 +3246,21 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>101</v>
@@ -3263,21 +3269,21 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>103</v>
@@ -3286,21 +3292,21 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>105</v>
@@ -3309,21 +3315,21 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>107</v>
@@ -3332,35 +3338,35 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>158</v>
@@ -3369,7 +3375,7 @@
         <v>27</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>159</v>
@@ -3378,12 +3384,12 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>160</v>
@@ -3392,7 +3398,7 @@
         <v>27</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>161</v>
@@ -3401,7 +3407,7 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="117">
@@ -3409,36 +3415,36 @@
         <v>164</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D117" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G117" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>127</v>
@@ -3452,7 +3458,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>128</v>
@@ -3461,7 +3467,7 @@
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>129</v>
@@ -3475,19 +3481,19 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -3498,7 +3504,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>168</v>
@@ -3507,7 +3513,7 @@
         <v>27</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>169</v>
@@ -3521,7 +3527,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>170</v>
@@ -3530,7 +3536,7 @@
         <v>27</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>171</v>
@@ -3544,7 +3550,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>172</v>
@@ -3553,7 +3559,7 @@
         <v>27</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>173</v>
@@ -3567,7 +3573,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>174</v>
@@ -3576,7 +3582,7 @@
         <v>27</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>175</v>
@@ -3590,7 +3596,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>176</v>
@@ -3599,7 +3605,7 @@
         <v>27</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>177</v>
@@ -3613,19 +3619,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="C126" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
@@ -3636,7 +3642,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>181</v>
@@ -3645,7 +3651,7 @@
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>182</v>
@@ -3659,53 +3665,53 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C128" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C128" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>187</v>
+        <v>18</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E129" s="2" t="s">
+      <c r="F129" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G129" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>190</v>
@@ -3714,7 +3720,7 @@
         <v>27</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>191</v>
@@ -3723,12 +3729,12 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>192</v>
@@ -3737,7 +3743,7 @@
         <v>27</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>193</v>
@@ -3746,12 +3752,12 @@
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>194</v>
@@ -3760,7 +3766,7 @@
         <v>27</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>195</v>
@@ -3769,12 +3775,12 @@
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>196</v>
@@ -3783,7 +3789,7 @@
         <v>27</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>197</v>
@@ -3792,12 +3798,12 @@
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>198</v>
@@ -3806,44 +3812,44 @@
         <v>27</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>201</v>
@@ -3852,44 +3858,44 @@
         <v>27</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>203</v>
+        <v>20</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>204</v>
@@ -3898,7 +3904,7 @@
         <v>27</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>205</v>
@@ -3907,12 +3913,12 @@
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>206</v>
@@ -3921,7 +3927,7 @@
         <v>27</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>207</v>
@@ -3930,12 +3936,12 @@
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>208</v>
@@ -3944,7 +3950,7 @@
         <v>27</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>209</v>
@@ -3953,44 +3959,44 @@
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="C141" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E141" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="F141" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B142" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D142" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>215</v>
@@ -4004,7 +4010,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>216</v>
@@ -4013,7 +4019,7 @@
         <v>27</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>217</v>
@@ -4022,6 +4028,29 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G144" s="2" t="s">
         <v>18</v>
       </c>
     </row>
